--- a/output/看屋檢查清單_新北建案_2026-09-04_一_基本資料.xlsx
+++ b/output/看屋檢查清單_新北建案_2026-09-04_一_基本資料.xlsx
@@ -231,7 +231,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>資料搜尋日期：2026-09-04　|　來源：591新建案／實價登錄、樂居、樂屋網、5168、住展、永慶、信義、PLEX、Mobile01、各建商官網、看屋部落格、新北市／台北市政府圖資　|　共用說明：①貸款試算＝貸8成/30年/利率2.5%（2026年五大行庫2.3~2.6%）；新青安3.0首購約1.775%、上限1,000萬 ②稅費＝契稅(房屋評定現值×6%)＋印花稅0.1%＋代書費1.5~2萬＋規費0.1%，概估總價1~1.5% ③預售屋法定保固：結構15年、固定建材設備1年，自交屋日起算 ④預售屋履約保證五擇一：價金返還保證／價金信託／不動產開發信託／同業連帶擔保／公會連帶保證 ⑤斷層：台北盆地列冊活動斷層僅山腳斷層(第二類，約1萬年前活動)，位於盆地西北側樹林—北投—金山一線 ⑥土壤液化：新北市已公布14區1/2500中級圖資(第1期板橋/新莊/三重/蘆洲/泰山/五股，第2期中和/永和/土城/鶯歌/三峽/樹林/新店/汐止)，查詢 liquid.net.tw/cgs/Web/Map.aspx；台北市查詢 soil.taipei（1/5000） ⑦淹水潛勢：第三代淹水潛勢圖（103-105年製），假設24小時降雨300/450/600mm之最大淹水深度，查詢國家災害防救科技中心 dmap.ncdr.nat.gov.tw；新北市水利局亦提供潛勢區/低窪區/洪氾區查詢 ⑧治安：引用網路整理之113年(2024)新北市各區犯罪率分級，非警政署原始表，僅供相對比較 ⑨【現場確認】標記＝公開資料查無、須至接待中心索取或調謄本之項目</t>
+          <t>資料搜尋日期：2026-09-04　|　來源：591／樂居／樂屋網／5168／住展／Mobile01／建商官網／政府圖資　|　【試算】貸8成30年2.5%；新青安1.775%上限1000萬｜稅費≒總價1~1.5%｜保固：結構15年、設備1年（自交屋起）｜履約保證法定五擇一｜斷層：北盆地僅山腳斷層(第二類)　|　【現場確認】＝公開資料查無，須向代銷索取或調謄本　|　查詢：土壤液化 liquid.net.tw／soil.taipei；淹水 dmap.ncdr.nat.gov.tw；新北液化圖資第1期板橋三重等、第2期中和土城新店等　|　治安為網路整理之113年新北各區犯罪率分級，非警政署原表　|　!＝風險提醒　+＝正面條件（原⚠️／✅）</t>
         </is>
       </c>
     </row>
@@ -413,7 +413,6 @@
               <sz val="10"/>
             </rPr>
             <t xml:space="preserve">
-→ 主結構屋齡以84~102年建物為準，非新成屋；外觀為重新拉皮、管線重拉
 建照／使照確切字號未公開，</t>
           </r>
           <r>
@@ -433,15 +432,16 @@
           </r>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <color rgb="FF000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">預售案，建照字號未公開
-</t>
+      <c r="D7" s="8" t="inlineStr"/>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="FF000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>分期推案（I台北公園／II紐約公園／III巴黎公園／IV英倫公園），各期建照分別請領
+確切字號未公開，</t>
           </r>
           <r>
             <rPr>
@@ -456,19 +456,24 @@
               <color rgb="FF000000"/>
               <sz val="10"/>
             </rPr>
-            <t>請代銷出示建造執照影本（預售屋須已請領建照方可銷售）</t>
-          </r>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <color rgb="FF000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>分期推案（I台北公園／II紐約公園／III巴黎公園／IV英倫公園），各期建照分別請領
-確切字號未公開，</t>
+            <t>請確認所看戶別隸屬哪一期並索取該期使照</t>
+          </r>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>；本案另申請耐震標章，可一併索取證書</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="FF000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">已完工社區，使照字號未公開
+</t>
           </r>
           <r>
             <rPr>
@@ -483,108 +488,32 @@
               <color rgb="FF000000"/>
               <sz val="10"/>
             </rPr>
-            <t>請確認所看戶別隸屬哪一期並索取該期使照</t>
-          </r>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <color rgb="FF000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">預售案，建照字號未公開
-</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
+            <t>可調閱建物謄本或向台北市建管處查詢；亦可向管委會索取</t>
+          </r>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="FF000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">捷運聯合開發案（與台北市捷運工程局合建），建照字號未公開
+</t>
+          </r>
+          <r>
+            <rPr>
               <color rgb="00C00000"/>
               <sz val="10"/>
             </rPr>
-            <t>【現場確認】</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FF000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>請代銷出示建造執照影本；本案另申請耐震標章，可一併索取證書</t>
-          </r>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <color rgb="FF000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">已完工社區，使照字號未公開
-</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>【現場確認】</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FF000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>可調閱建物謄本或向台北市建管處查詢；亦可向管委會索取</t>
-          </r>
-        </is>
-      </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <color rgb="FF000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">捷運聯合開發案（與台北市捷運工程局合建），建照字號未公開
-</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
             <t>⚠️聯開宅之產權與一般自地自建不同，【現場確認】務必確認基地為捷運局土地、取得方式（地上權或所有權）與分回比例</t>
           </r>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <color rgb="FF000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">預售案，建照字號未公開；建築設計為A8聯合建築師事務所
-</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>【現場確認】</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FF000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>請代銷出示建造執照影本</t>
-          </r>
+          <t>；建築設計為A8聯合建築師事務所</t>
         </is>
       </c>
     </row>
@@ -773,7 +702,6 @@
             </rPr>
             <t xml:space="preserve">共195戶住家＋1戶店面（另有來源記196戶）
 A、B、C棟地上5層/地下1~2層；E棟地上3層/地下1層
-A、B棟單層各14、15戶配2部電梯；C棟每層8戶配1部電梯
 </t>
           </r>
           <r>
@@ -789,7 +717,6 @@
         <is>
           <t>地上12層、地下3層
 共95戶（住家91戶+店面2戶+辦公2戶）
-1~5F為捷運站體，6~12F為住宅
 單層13戶配2部電梯（梯戶比約1:48）</t>
         </is>
       </c>
@@ -809,8 +736,6 @@
             </rPr>
             <t xml:space="preserve">
 ・樂屋網：總戶數1,297戶
-・多數來源：1,275戶住家＋21戶店面（合計1,296戶）
-・另有「4幢7棟、1,296戶」說法
 棟數：A~F棟（A~D棟地上27層、E/F棟地上15層），地下6層</t>
           </r>
         </is>
@@ -936,22 +861,6 @@
               <sz val="10"/>
             </rPr>
             <t xml:space="preserve">套房14~15坪、1房1衛19坪
-</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="001F4E78"/>
-              <sz val="10"/>
-            </rPr>
-            <t>2房1衛23~24坪、2房2衛31坪、3房2衛32~33坪</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FF000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
 </t>
           </r>
           <r>
